--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2488074_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2488074_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>4.6303</v>
+        <v>4.8017</v>
       </c>
       <c r="E2" t="n">
-        <v>2.3682</v>
+        <v>2.7362</v>
       </c>
       <c r="F2" t="n">
-        <v>2.2621</v>
+        <v>2.0655</v>
       </c>
       <c r="G2" t="n">
         <v>0.382</v>
@@ -610,13 +610,13 @@
         <v>2.7751</v>
       </c>
       <c r="S2" t="n">
-        <v>0.6288</v>
+        <v>0.8002</v>
       </c>
       <c r="T2" t="n">
-        <v>-0.8184</v>
+        <v>-0.4504</v>
       </c>
       <c r="U2" t="n">
-        <v>1.4472</v>
+        <v>1.2506</v>
       </c>
       <c r="V2" t="n">
         <v>2.8267</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>2.9019</v>
+        <v>3.6349</v>
       </c>
       <c r="E3" t="n">
-        <v>2.4166</v>
+        <v>2.7846</v>
       </c>
       <c r="F3" t="n">
-        <v>0.4853</v>
+        <v>0.8502999999999999</v>
       </c>
       <c r="G3" t="n">
         <v>2.6314</v>
@@ -688,13 +688,13 @@
         <v>0.9911</v>
       </c>
       <c r="S3" t="n">
-        <v>-0.4541</v>
+        <v>0.279</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.9873</v>
+        <v>-0.6193</v>
       </c>
       <c r="U3" t="n">
-        <v>0.5333</v>
+        <v>0.8983</v>
       </c>
       <c r="V3" t="n">
         <v>-0.2666</v>
@@ -709,7 +709,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>P. AVALOS ORTIZ</t>
+          <t>L. SIGISMONTI RODRÍGUEZ</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,73 +721,73 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>1.5628</v>
+        <v>1.508</v>
       </c>
       <c r="E4" t="n">
-        <v>0.9319</v>
+        <v>1.508</v>
       </c>
       <c r="F4" t="n">
-        <v>0.6308</v>
+        <v>0</v>
       </c>
       <c r="G4" t="n">
-        <v>-0.2402</v>
+        <v>1.508</v>
       </c>
       <c r="H4" t="n">
-        <v>-0.7529</v>
+        <v>0.3027</v>
       </c>
       <c r="I4" t="n">
-        <v>0.5127</v>
+        <v>1.2053</v>
       </c>
       <c r="J4" t="n">
-        <v>1.8845</v>
+        <v>1.508</v>
       </c>
       <c r="K4" t="n">
-        <v>1.1172</v>
+        <v>0.3027</v>
       </c>
       <c r="L4" t="n">
-        <v>0.7673</v>
+        <v>1.2053</v>
       </c>
       <c r="M4" t="n">
-        <v>-2.1247</v>
+        <v>0</v>
       </c>
       <c r="N4" t="n">
-        <v>-1.8702</v>
+        <v>0</v>
       </c>
       <c r="O4" t="n">
-        <v>-0.2545</v>
+        <v>0</v>
       </c>
       <c r="P4" t="n">
-        <v>-0.1982</v>
+        <v>0</v>
       </c>
       <c r="Q4" t="n">
-        <v>-1.9822</v>
+        <v>0</v>
       </c>
       <c r="R4" t="n">
-        <v>1.784</v>
+        <v>0</v>
       </c>
       <c r="S4" t="n">
-        <v>0.1905</v>
+        <v>0</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.444</v>
+        <v>0</v>
       </c>
       <c r="U4" t="n">
-        <v>0.6346000000000001</v>
+        <v>0</v>
       </c>
       <c r="V4" t="n">
-        <v>1.8107</v>
+        <v>0</v>
       </c>
       <c r="W4" t="n">
-        <v>1.4737</v>
+        <v>0</v>
       </c>
       <c r="X4" t="n">
-        <v>0.337</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>L. SIGISMONTI RODRÍGUEZ</t>
+          <t>P. AVALOS ORTIZ</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,73 +799,73 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>1.508</v>
+        <v>1.4328</v>
       </c>
       <c r="E5" t="n">
-        <v>1.508</v>
+        <v>0.8300999999999999</v>
       </c>
       <c r="F5" t="n">
-        <v>0</v>
+        <v>0.6028</v>
       </c>
       <c r="G5" t="n">
-        <v>1.508</v>
+        <v>-0.2402</v>
       </c>
       <c r="H5" t="n">
-        <v>0.3027</v>
+        <v>-0.7529</v>
       </c>
       <c r="I5" t="n">
-        <v>1.2053</v>
+        <v>0.5127</v>
       </c>
       <c r="J5" t="n">
-        <v>1.508</v>
+        <v>1.8845</v>
       </c>
       <c r="K5" t="n">
-        <v>0.3027</v>
+        <v>1.1172</v>
       </c>
       <c r="L5" t="n">
-        <v>1.2053</v>
+        <v>0.7673</v>
       </c>
       <c r="M5" t="n">
-        <v>0</v>
+        <v>-2.1247</v>
       </c>
       <c r="N5" t="n">
-        <v>0</v>
+        <v>-1.8702</v>
       </c>
       <c r="O5" t="n">
-        <v>0</v>
+        <v>-0.2545</v>
       </c>
       <c r="P5" t="n">
-        <v>0</v>
+        <v>-0.1982</v>
       </c>
       <c r="Q5" t="n">
-        <v>0</v>
+        <v>-1.9822</v>
       </c>
       <c r="R5" t="n">
-        <v>0</v>
+        <v>1.784</v>
       </c>
       <c r="S5" t="n">
-        <v>0</v>
+        <v>0.0606</v>
       </c>
       <c r="T5" t="n">
-        <v>0</v>
+        <v>-0.5459000000000001</v>
       </c>
       <c r="U5" t="n">
-        <v>0</v>
+        <v>0.6065</v>
       </c>
       <c r="V5" t="n">
-        <v>0</v>
+        <v>1.8107</v>
       </c>
       <c r="W5" t="n">
-        <v>0</v>
+        <v>1.4737</v>
       </c>
       <c r="X5" t="n">
-        <v>0</v>
+        <v>0.337</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>J. VALEIRAS CREUS</t>
+          <t>P. TRUNO SOMS</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,73 +877,73 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>1.4331</v>
+        <v>0.9371</v>
       </c>
       <c r="E6" t="n">
-        <v>-1.0974</v>
+        <v>0.228</v>
       </c>
       <c r="F6" t="n">
-        <v>2.5306</v>
+        <v>0.7091</v>
       </c>
       <c r="G6" t="n">
-        <v>0.6028</v>
+        <v>-1.4294</v>
       </c>
       <c r="H6" t="n">
-        <v>1.1098</v>
+        <v>-0.7752</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.507</v>
+        <v>-0.6542</v>
       </c>
       <c r="J6" t="n">
-        <v>1.0491</v>
+        <v>0.2297</v>
       </c>
       <c r="K6" t="n">
-        <v>1.5675</v>
+        <v>0.222</v>
       </c>
       <c r="L6" t="n">
-        <v>-0.5184</v>
+        <v>0.0078</v>
       </c>
       <c r="M6" t="n">
-        <v>-0.4463</v>
+        <v>-1.6591</v>
       </c>
       <c r="N6" t="n">
-        <v>-0.4577</v>
+        <v>-0.9971</v>
       </c>
       <c r="O6" t="n">
-        <v>0.0114</v>
+        <v>-0.662</v>
       </c>
       <c r="P6" t="n">
-        <v>-0.9911</v>
+        <v>1.784</v>
       </c>
       <c r="Q6" t="n">
-        <v>-2.9733</v>
+        <v>0</v>
       </c>
       <c r="R6" t="n">
-        <v>1.9822</v>
+        <v>1.784</v>
       </c>
       <c r="S6" t="n">
-        <v>1.8718</v>
+        <v>0.3662</v>
       </c>
       <c r="T6" t="n">
-        <v>1.1638</v>
+        <v>-0.0017</v>
       </c>
       <c r="U6" t="n">
-        <v>0.708</v>
+        <v>0.3679</v>
       </c>
       <c r="V6" t="n">
-        <v>-0.0503</v>
+        <v>0.2163</v>
       </c>
       <c r="W6" t="n">
-        <v>-0.337</v>
+        <v>0</v>
       </c>
       <c r="X6" t="n">
-        <v>0.2867</v>
+        <v>0.2163</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>D. MELERO ZURITA</t>
+          <t>P. ÁVALOS ORTIZ</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,67 +955,67 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>0.9562</v>
+        <v>0.9053</v>
       </c>
       <c r="E7" t="n">
-        <v>0.2013</v>
+        <v>0.9053</v>
       </c>
       <c r="F7" t="n">
-        <v>0.7549</v>
+        <v>0</v>
       </c>
       <c r="G7" t="n">
-        <v>-0.2387</v>
+        <v>0.9053</v>
       </c>
       <c r="H7" t="n">
-        <v>-2.655</v>
+        <v>0.3027</v>
       </c>
       <c r="I7" t="n">
-        <v>2.4164</v>
+        <v>0.6027</v>
       </c>
       <c r="J7" t="n">
-        <v>1.1335</v>
+        <v>0.9053</v>
       </c>
       <c r="K7" t="n">
-        <v>-1.526</v>
+        <v>0.3027</v>
       </c>
       <c r="L7" t="n">
-        <v>2.6595</v>
+        <v>0.6027</v>
       </c>
       <c r="M7" t="n">
-        <v>-1.3722</v>
+        <v>0</v>
       </c>
       <c r="N7" t="n">
-        <v>-1.129</v>
+        <v>0</v>
       </c>
       <c r="O7" t="n">
-        <v>-0.2431</v>
+        <v>0</v>
       </c>
       <c r="P7" t="n">
-        <v>0.5947</v>
+        <v>0</v>
       </c>
       <c r="Q7" t="n">
-        <v>-0.9911</v>
+        <v>0</v>
       </c>
       <c r="R7" t="n">
-        <v>1.5858</v>
+        <v>0</v>
       </c>
       <c r="S7" t="n">
-        <v>0.8668</v>
+        <v>0</v>
       </c>
       <c r="T7" t="n">
-        <v>0.0589</v>
+        <v>0</v>
       </c>
       <c r="U7" t="n">
-        <v>0.8078</v>
+        <v>0</v>
       </c>
       <c r="V7" t="n">
-        <v>-0.2666</v>
+        <v>0</v>
       </c>
       <c r="W7" t="n">
         <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>-0.2666</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8">
@@ -1033,13 +1033,13 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>0.9266</v>
+        <v>0.7643</v>
       </c>
       <c r="E8" t="n">
-        <v>2.3039</v>
+        <v>2.3663</v>
       </c>
       <c r="F8" t="n">
-        <v>-1.3773</v>
+        <v>-1.6019</v>
       </c>
       <c r="G8" t="n">
         <v>0.6463</v>
@@ -1078,13 +1078,13 @@
         <v>0.3964</v>
       </c>
       <c r="S8" t="n">
-        <v>1.091</v>
+        <v>0.9287</v>
       </c>
       <c r="T8" t="n">
-        <v>0.1286</v>
+        <v>0.191</v>
       </c>
       <c r="U8" t="n">
-        <v>0.9624</v>
+        <v>0.7377</v>
       </c>
       <c r="V8" t="n">
         <v>-1.2071</v>
@@ -1099,7 +1099,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>P. ÁVALOS ORTIZ</t>
+          <t>D. MELERO ZURITA</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,73 +1111,73 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>0.9053</v>
+        <v>0.7161999999999999</v>
       </c>
       <c r="E9" t="n">
-        <v>0.9053</v>
+        <v>-0.3475</v>
       </c>
       <c r="F9" t="n">
-        <v>0</v>
+        <v>1.0637</v>
       </c>
       <c r="G9" t="n">
-        <v>0.9053</v>
+        <v>-0.2387</v>
       </c>
       <c r="H9" t="n">
-        <v>0.3027</v>
+        <v>-2.655</v>
       </c>
       <c r="I9" t="n">
-        <v>0.6027</v>
+        <v>2.4164</v>
       </c>
       <c r="J9" t="n">
-        <v>0.9053</v>
+        <v>1.1335</v>
       </c>
       <c r="K9" t="n">
-        <v>0.3027</v>
+        <v>-1.526</v>
       </c>
       <c r="L9" t="n">
-        <v>0.6027</v>
+        <v>2.6595</v>
       </c>
       <c r="M9" t="n">
-        <v>0</v>
+        <v>-1.3722</v>
       </c>
       <c r="N9" t="n">
-        <v>0</v>
+        <v>-1.129</v>
       </c>
       <c r="O9" t="n">
-        <v>0</v>
+        <v>-0.2431</v>
       </c>
       <c r="P9" t="n">
-        <v>0</v>
+        <v>0.5947</v>
       </c>
       <c r="Q9" t="n">
-        <v>0</v>
+        <v>-0.9911</v>
       </c>
       <c r="R9" t="n">
-        <v>0</v>
+        <v>1.5858</v>
       </c>
       <c r="S9" t="n">
-        <v>0</v>
+        <v>0.6268</v>
       </c>
       <c r="T9" t="n">
-        <v>0</v>
+        <v>-0.4899</v>
       </c>
       <c r="U9" t="n">
-        <v>0</v>
+        <v>1.1167</v>
       </c>
       <c r="V9" t="n">
-        <v>0</v>
+        <v>-0.2666</v>
       </c>
       <c r="W9" t="n">
         <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>0</v>
+        <v>-0.2666</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>P. TRUÑO SOMS</t>
+          <t>J. CEBOLLA HERRERA</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,73 +1189,73 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>0.6027</v>
+        <v>0.6526</v>
       </c>
       <c r="E10" t="n">
-        <v>0.6027</v>
+        <v>2.7155</v>
       </c>
       <c r="F10" t="n">
-        <v>0</v>
+        <v>-2.0629</v>
       </c>
       <c r="G10" t="n">
-        <v>0.6027</v>
+        <v>1.094</v>
       </c>
       <c r="H10" t="n">
-        <v>0</v>
+        <v>0.0551</v>
       </c>
       <c r="I10" t="n">
-        <v>0.6027</v>
+        <v>1.0389</v>
       </c>
       <c r="J10" t="n">
-        <v>0.6027</v>
+        <v>2.9549</v>
       </c>
       <c r="K10" t="n">
-        <v>0</v>
+        <v>1.6615</v>
       </c>
       <c r="L10" t="n">
-        <v>0.6027</v>
+        <v>1.2935</v>
       </c>
       <c r="M10" t="n">
-        <v>0</v>
+        <v>-1.8609</v>
       </c>
       <c r="N10" t="n">
-        <v>0</v>
+        <v>-1.6064</v>
       </c>
       <c r="O10" t="n">
-        <v>0</v>
+        <v>-0.2545</v>
       </c>
       <c r="P10" t="n">
-        <v>0</v>
+        <v>1.1893</v>
       </c>
       <c r="Q10" t="n">
         <v>0</v>
       </c>
       <c r="R10" t="n">
-        <v>0</v>
+        <v>1.1893</v>
       </c>
       <c r="S10" t="n">
-        <v>0</v>
+        <v>0.1799</v>
       </c>
       <c r="T10" t="n">
-        <v>0</v>
+        <v>-0.2394</v>
       </c>
       <c r="U10" t="n">
-        <v>0</v>
+        <v>0.4193</v>
       </c>
       <c r="V10" t="n">
-        <v>0</v>
+        <v>-1.8107</v>
       </c>
       <c r="W10" t="n">
         <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>0</v>
+        <v>-1.8107</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>J. CEBOLLA HERRERA</t>
+          <t>P. TRUÑO SOMS</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1267,73 +1267,73 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>0.3959</v>
+        <v>0.6027</v>
       </c>
       <c r="E11" t="n">
-        <v>2.2062</v>
+        <v>0.6027</v>
       </c>
       <c r="F11" t="n">
-        <v>-1.8102</v>
+        <v>0</v>
       </c>
       <c r="G11" t="n">
-        <v>1.094</v>
+        <v>0.6027</v>
       </c>
       <c r="H11" t="n">
-        <v>0.0551</v>
+        <v>0</v>
       </c>
       <c r="I11" t="n">
-        <v>1.0389</v>
+        <v>0.6027</v>
       </c>
       <c r="J11" t="n">
-        <v>2.9549</v>
+        <v>0.6027</v>
       </c>
       <c r="K11" t="n">
-        <v>1.6615</v>
+        <v>0</v>
       </c>
       <c r="L11" t="n">
-        <v>1.2935</v>
+        <v>0.6027</v>
       </c>
       <c r="M11" t="n">
-        <v>-1.8609</v>
+        <v>0</v>
       </c>
       <c r="N11" t="n">
-        <v>-1.6064</v>
+        <v>0</v>
       </c>
       <c r="O11" t="n">
-        <v>-0.2545</v>
+        <v>0</v>
       </c>
       <c r="P11" t="n">
-        <v>1.1893</v>
+        <v>0</v>
       </c>
       <c r="Q11" t="n">
         <v>0</v>
       </c>
       <c r="R11" t="n">
-        <v>1.1893</v>
+        <v>0</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.07679999999999999</v>
+        <v>0</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.7488</v>
+        <v>0</v>
       </c>
       <c r="U11" t="n">
-        <v>0.672</v>
+        <v>0</v>
       </c>
       <c r="V11" t="n">
-        <v>-1.8107</v>
+        <v>0</v>
       </c>
       <c r="W11" t="n">
         <v>0</v>
       </c>
       <c r="X11" t="n">
-        <v>-1.8107</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>M. BOTAS FERNANDEZ</t>
+          <t>J. VALEIRAS CREUS</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1345,73 +1345,73 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>0.3379</v>
+        <v>0.5506</v>
       </c>
       <c r="E12" t="n">
-        <v>3.699</v>
+        <v>-1.9518</v>
       </c>
       <c r="F12" t="n">
-        <v>-3.3611</v>
+        <v>2.5025</v>
       </c>
       <c r="G12" t="n">
-        <v>4.027</v>
+        <v>0.6028</v>
       </c>
       <c r="H12" t="n">
-        <v>3.6576</v>
+        <v>1.1098</v>
       </c>
       <c r="I12" t="n">
-        <v>0.3694</v>
+        <v>-0.507</v>
       </c>
       <c r="J12" t="n">
-        <v>5.2729</v>
+        <v>1.0491</v>
       </c>
       <c r="K12" t="n">
-        <v>4.6547</v>
+        <v>1.5675</v>
       </c>
       <c r="L12" t="n">
-        <v>0.6182</v>
+        <v>-0.5184</v>
       </c>
       <c r="M12" t="n">
-        <v>-1.246</v>
+        <v>-0.4463</v>
       </c>
       <c r="N12" t="n">
-        <v>-0.9971</v>
+        <v>-0.4577</v>
       </c>
       <c r="O12" t="n">
-        <v>-0.2488</v>
+        <v>0.0114</v>
       </c>
       <c r="P12" t="n">
-        <v>0.1982</v>
+        <v>-0.9911</v>
       </c>
       <c r="Q12" t="n">
-        <v>-0.9911</v>
+        <v>-2.9733</v>
       </c>
       <c r="R12" t="n">
-        <v>1.1893</v>
+        <v>1.9822</v>
       </c>
       <c r="S12" t="n">
-        <v>1.2781</v>
+        <v>0.9893</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.2458</v>
+        <v>0.3094</v>
       </c>
       <c r="U12" t="n">
-        <v>1.5239</v>
+        <v>0.6798999999999999</v>
       </c>
       <c r="V12" t="n">
-        <v>-5.1654</v>
+        <v>-0.0503</v>
       </c>
       <c r="W12" t="n">
         <v>-0.337</v>
       </c>
       <c r="X12" t="n">
-        <v>-4.8284</v>
+        <v>0.2867</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>D. JUZBASIC</t>
+          <t>M. BOTAS FERNANDEZ</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1423,73 +1423,73 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>0.1593</v>
+        <v>-0.0281</v>
       </c>
       <c r="E13" t="n">
-        <v>0.8546</v>
+        <v>3.5577</v>
       </c>
       <c r="F13" t="n">
-        <v>-0.6953</v>
+        <v>-3.5857</v>
       </c>
       <c r="G13" t="n">
-        <v>-0.1257</v>
+        <v>4.027</v>
       </c>
       <c r="H13" t="n">
-        <v>2.0916</v>
+        <v>3.6576</v>
       </c>
       <c r="I13" t="n">
-        <v>-2.2173</v>
+        <v>0.3694</v>
       </c>
       <c r="J13" t="n">
-        <v>0.2625</v>
+        <v>5.2729</v>
       </c>
       <c r="K13" t="n">
-        <v>2.2195</v>
+        <v>4.6547</v>
       </c>
       <c r="L13" t="n">
-        <v>-1.957</v>
+        <v>0.6182</v>
       </c>
       <c r="M13" t="n">
-        <v>-0.3882</v>
+        <v>-1.246</v>
       </c>
       <c r="N13" t="n">
-        <v>-0.128</v>
+        <v>-0.9971</v>
       </c>
       <c r="O13" t="n">
-        <v>-0.2602</v>
+        <v>-0.2488</v>
       </c>
       <c r="P13" t="n">
-        <v>-0.1982</v>
+        <v>0.1982</v>
       </c>
       <c r="Q13" t="n">
         <v>-0.9911</v>
       </c>
       <c r="R13" t="n">
-        <v>0.7929</v>
+        <v>1.1893</v>
       </c>
       <c r="S13" t="n">
-        <v>0.6743</v>
+        <v>0.9122</v>
       </c>
       <c r="T13" t="n">
-        <v>0.18</v>
+        <v>-0.3871</v>
       </c>
       <c r="U13" t="n">
-        <v>0.4944</v>
+        <v>1.2993</v>
       </c>
       <c r="V13" t="n">
-        <v>-0.1911</v>
+        <v>-5.1654</v>
       </c>
       <c r="W13" t="n">
-        <v>1.4033</v>
+        <v>-0.337</v>
       </c>
       <c r="X13" t="n">
-        <v>-1.5944</v>
+        <v>-4.8284</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>P. TRUNO SOMS</t>
+          <t>D. JUZBASIC</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1501,67 +1501,67 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>0.0045</v>
+        <v>-0.27</v>
       </c>
       <c r="E14" t="n">
-        <v>-0.508</v>
+        <v>0.5095</v>
       </c>
       <c r="F14" t="n">
-        <v>0.5125</v>
+        <v>-0.7796</v>
       </c>
       <c r="G14" t="n">
-        <v>-1.4294</v>
+        <v>-0.1257</v>
       </c>
       <c r="H14" t="n">
-        <v>-0.7752</v>
+        <v>2.0916</v>
       </c>
       <c r="I14" t="n">
-        <v>-0.6542</v>
+        <v>-2.2173</v>
       </c>
       <c r="J14" t="n">
-        <v>0.2297</v>
+        <v>0.2625</v>
       </c>
       <c r="K14" t="n">
-        <v>0.222</v>
+        <v>2.2195</v>
       </c>
       <c r="L14" t="n">
-        <v>0.0078</v>
+        <v>-1.957</v>
       </c>
       <c r="M14" t="n">
-        <v>-1.6591</v>
+        <v>-0.3882</v>
       </c>
       <c r="N14" t="n">
-        <v>-0.9971</v>
+        <v>-0.128</v>
       </c>
       <c r="O14" t="n">
-        <v>-0.662</v>
+        <v>-0.2602</v>
       </c>
       <c r="P14" t="n">
-        <v>1.784</v>
+        <v>-0.1982</v>
       </c>
       <c r="Q14" t="n">
-        <v>0</v>
+        <v>-0.9911</v>
       </c>
       <c r="R14" t="n">
-        <v>1.784</v>
+        <v>0.7929</v>
       </c>
       <c r="S14" t="n">
-        <v>-0.5664</v>
+        <v>0.245</v>
       </c>
       <c r="T14" t="n">
-        <v>-0.7377</v>
+        <v>-0.1651</v>
       </c>
       <c r="U14" t="n">
-        <v>0.1714</v>
+        <v>0.4102</v>
       </c>
       <c r="V14" t="n">
-        <v>0.2163</v>
+        <v>-0.1911</v>
       </c>
       <c r="W14" t="n">
-        <v>0</v>
+        <v>1.4033</v>
       </c>
       <c r="X14" t="n">
-        <v>0.2163</v>
+        <v>-1.5944</v>
       </c>
     </row>
     <row r="15">
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>-2.9567</v>
+        <v>-2.2165</v>
       </c>
       <c r="E15" t="n">
-        <v>-3.1866</v>
+        <v>-2.6149</v>
       </c>
       <c r="F15" t="n">
-        <v>0.2299</v>
+        <v>0.3983</v>
       </c>
       <c r="G15" t="n">
         <v>-1.0286</v>
@@ -1624,13 +1624,13 @@
         <v>1.3876</v>
       </c>
       <c r="S15" t="n">
-        <v>-0.8054</v>
+        <v>-0.06519999999999999</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.6864</v>
+        <v>-0.1146</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.119</v>
+        <v>0.0495</v>
       </c>
       <c r="V15" t="n">
         <v>-0.5281</v>
@@ -1657,25 +1657,25 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>13.3678</v>
+        <v>13.99160000000001</v>
       </c>
       <c r="E16" t="n">
-        <v>13.20570000000001</v>
+        <v>13.8297</v>
       </c>
       <c r="F16" t="n">
-        <v>0.1622000000000003</v>
+        <v>0.1621000000000001</v>
       </c>
       <c r="G16" t="n">
         <v>9.3369</v>
       </c>
       <c r="H16" t="n">
-        <v>2.7168</v>
+        <v>2.716800000000001</v>
       </c>
       <c r="I16" t="n">
-        <v>6.6203</v>
+        <v>6.620300000000001</v>
       </c>
       <c r="J16" t="n">
-        <v>23.4932</v>
+        <v>23.49319999999999</v>
       </c>
       <c r="K16" t="n">
         <v>14.3562</v>
@@ -1702,16 +1702,16 @@
         <v>15.8577</v>
       </c>
       <c r="S16" t="n">
-        <v>4.6986</v>
+        <v>5.3227</v>
       </c>
       <c r="T16" t="n">
-        <v>-3.1371</v>
+        <v>-2.512999999999999</v>
       </c>
       <c r="U16" t="n">
-        <v>7.836</v>
+        <v>7.8359</v>
       </c>
       <c r="V16" t="n">
-        <v>-4.632199999999999</v>
+        <v>-4.6322</v>
       </c>
       <c r="W16" t="n">
         <v>4.743</v>
@@ -1723,7 +1723,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>D. GARCÍA GAZQUEZ</t>
+          <t>H. TAVIO SOLIS</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,73 +1735,73 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>3.324</v>
+        <v>3.436</v>
       </c>
       <c r="E17" t="n">
-        <v>3.324</v>
+        <v>2.7078</v>
       </c>
       <c r="F17" t="n">
-        <v>0</v>
+        <v>0.7282</v>
       </c>
       <c r="G17" t="n">
-        <v>3.324</v>
+        <v>-0.3689</v>
       </c>
       <c r="H17" t="n">
-        <v>2.1187</v>
+        <v>-0.0876</v>
       </c>
       <c r="I17" t="n">
-        <v>1.2053</v>
+        <v>-0.2812</v>
       </c>
       <c r="J17" t="n">
-        <v>3.324</v>
+        <v>1.0168</v>
       </c>
       <c r="K17" t="n">
-        <v>2.1187</v>
+        <v>1.0492</v>
       </c>
       <c r="L17" t="n">
-        <v>1.2053</v>
+        <v>-0.0324</v>
       </c>
       <c r="M17" t="n">
-        <v>0</v>
+        <v>-1.3857</v>
       </c>
       <c r="N17" t="n">
-        <v>0</v>
+        <v>-1.1369</v>
       </c>
       <c r="O17" t="n">
-        <v>0</v>
+        <v>-0.2488</v>
       </c>
       <c r="P17" t="n">
-        <v>0</v>
+        <v>0.9911</v>
       </c>
       <c r="Q17" t="n">
         <v>0</v>
       </c>
       <c r="R17" t="n">
-        <v>0</v>
+        <v>0.9911</v>
       </c>
       <c r="S17" t="n">
-        <v>0</v>
+        <v>-0.2744</v>
       </c>
       <c r="T17" t="n">
-        <v>0</v>
+        <v>-0.3863</v>
       </c>
       <c r="U17" t="n">
-        <v>0</v>
+        <v>0.1119</v>
       </c>
       <c r="V17" t="n">
-        <v>0</v>
+        <v>3.0882</v>
       </c>
       <c r="W17" t="n">
-        <v>0</v>
+        <v>2.0772</v>
       </c>
       <c r="X17" t="n">
-        <v>0</v>
+        <v>1.0109</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>H. TAVIO SOLIS</t>
+          <t>D. GARCÍA GAZQUEZ</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,67 +1813,67 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>3.0298</v>
+        <v>3.324</v>
       </c>
       <c r="E18" t="n">
-        <v>2.6059</v>
+        <v>3.324</v>
       </c>
       <c r="F18" t="n">
-        <v>0.4239</v>
+        <v>0</v>
       </c>
       <c r="G18" t="n">
-        <v>-0.3689</v>
+        <v>3.324</v>
       </c>
       <c r="H18" t="n">
-        <v>-0.0876</v>
+        <v>2.1187</v>
       </c>
       <c r="I18" t="n">
-        <v>-0.2812</v>
+        <v>1.2053</v>
       </c>
       <c r="J18" t="n">
-        <v>1.0168</v>
+        <v>3.324</v>
       </c>
       <c r="K18" t="n">
-        <v>1.0492</v>
+        <v>2.1187</v>
       </c>
       <c r="L18" t="n">
-        <v>-0.0324</v>
+        <v>1.2053</v>
       </c>
       <c r="M18" t="n">
-        <v>-1.3857</v>
+        <v>0</v>
       </c>
       <c r="N18" t="n">
-        <v>-1.1369</v>
+        <v>0</v>
       </c>
       <c r="O18" t="n">
-        <v>-0.2488</v>
+        <v>0</v>
       </c>
       <c r="P18" t="n">
-        <v>0.9911</v>
+        <v>0</v>
       </c>
       <c r="Q18" t="n">
         <v>0</v>
       </c>
       <c r="R18" t="n">
-        <v>0.9911</v>
+        <v>0</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.6806</v>
+        <v>0</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.4881</v>
+        <v>0</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.1924</v>
+        <v>0</v>
       </c>
       <c r="V18" t="n">
-        <v>3.0882</v>
+        <v>0</v>
       </c>
       <c r="W18" t="n">
-        <v>2.0772</v>
+        <v>0</v>
       </c>
       <c r="X18" t="n">
-        <v>1.0109</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -1891,13 +1891,13 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>0.7076</v>
+        <v>0.9288999999999999</v>
       </c>
       <c r="E19" t="n">
-        <v>1.9841</v>
+        <v>2.2897</v>
       </c>
       <c r="F19" t="n">
-        <v>-1.2765</v>
+        <v>-1.3607</v>
       </c>
       <c r="G19" t="n">
         <v>0.6588000000000001</v>
@@ -1936,13 +1936,13 @@
         <v>0.7929</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.1406</v>
+        <v>0.0808</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.9249000000000001</v>
+        <v>-0.6193</v>
       </c>
       <c r="U19" t="n">
-        <v>0.7843</v>
+        <v>0.7000999999999999</v>
       </c>
       <c r="V19" t="n">
         <v>-0.6036</v>
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>0.1208</v>
+        <v>-0.0209</v>
       </c>
       <c r="E20" t="n">
-        <v>3.004</v>
+        <v>2.6984</v>
       </c>
       <c r="F20" t="n">
-        <v>-2.8832</v>
+        <v>-2.7193</v>
       </c>
       <c r="G20" t="n">
         <v>-0.4412</v>
@@ -2014,13 +2014,13 @@
         <v>1.1893</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.6273</v>
+        <v>-0.769</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.8698</v>
+        <v>-1.1754</v>
       </c>
       <c r="U20" t="n">
-        <v>0.2425</v>
+        <v>0.4064</v>
       </c>
       <c r="V20" t="n">
         <v>0</v>
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-0.4098</v>
+        <v>-0.5548</v>
       </c>
       <c r="E21" t="n">
         <v>-0.295</v>
       </c>
       <c r="F21" t="n">
-        <v>-0.1148</v>
+        <v>-0.2598</v>
       </c>
       <c r="G21" t="n">
         <v>1.3254</v>
@@ -2092,13 +2092,13 @@
         <v>1.5858</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.6388</v>
+        <v>-0.7838000000000001</v>
       </c>
       <c r="T21" t="n">
         <v>-1.0497</v>
       </c>
       <c r="U21" t="n">
-        <v>0.4109</v>
+        <v>0.266</v>
       </c>
       <c r="V21" t="n">
         <v>2.2734</v>
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-1.813</v>
+        <v>-1.5368</v>
       </c>
       <c r="E22" t="n">
         <v>-2.1733</v>
       </c>
       <c r="F22" t="n">
-        <v>0.3603</v>
+        <v>0.6365</v>
       </c>
       <c r="G22" t="n">
         <v>0.2004</v>
@@ -2170,13 +2170,13 @@
         <v>0.3964</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.4276</v>
+        <v>-0.1514</v>
       </c>
       <c r="T22" t="n">
         <v>-0.312</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.1157</v>
+        <v>0.1606</v>
       </c>
       <c r="V22" t="n">
         <v>0</v>
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-2.3859</v>
+        <v>-2.0313</v>
       </c>
       <c r="E23" t="n">
-        <v>0.5295</v>
+        <v>0.6313</v>
       </c>
       <c r="F23" t="n">
-        <v>-2.9154</v>
+        <v>-2.6627</v>
       </c>
       <c r="G23" t="n">
         <v>-0.4685</v>
@@ -2248,13 +2248,13 @@
         <v>0.9911</v>
       </c>
       <c r="S23" t="n">
-        <v>-1.3842</v>
+        <v>-1.0296</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.9360000000000001</v>
+        <v>-0.8341</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.4483</v>
+        <v>-0.1956</v>
       </c>
       <c r="V23" t="n">
         <v>-0.5331</v>
@@ -2281,13 +2281,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-2.6683</v>
+        <v>-2.4867</v>
       </c>
       <c r="E24" t="n">
-        <v>-1.7963</v>
+        <v>-1.6944</v>
       </c>
       <c r="F24" t="n">
-        <v>-0.872</v>
+        <v>-0.7923</v>
       </c>
       <c r="G24" t="n">
         <v>-3.144</v>
@@ -2326,13 +2326,13 @@
         <v>1.3876</v>
       </c>
       <c r="S24" t="n">
-        <v>-0.2577</v>
+        <v>-0.0762</v>
       </c>
       <c r="T24" t="n">
-        <v>-0.9139</v>
+        <v>-0.8120000000000001</v>
       </c>
       <c r="U24" t="n">
-        <v>0.6562</v>
+        <v>0.7358</v>
       </c>
       <c r="V24" t="n">
         <v>0.337</v>
@@ -2359,13 +2359,13 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-3.7923</v>
+        <v>-3.392</v>
       </c>
       <c r="E25" t="n">
-        <v>-1.8897</v>
+        <v>-1.686</v>
       </c>
       <c r="F25" t="n">
-        <v>-1.9026</v>
+        <v>-1.7061</v>
       </c>
       <c r="G25" t="n">
         <v>-2.2714</v>
@@ -2404,13 +2404,13 @@
         <v>0.7929</v>
       </c>
       <c r="S25" t="n">
-        <v>-0.4526</v>
+        <v>-0.0523</v>
       </c>
       <c r="T25" t="n">
-        <v>-0.4881</v>
+        <v>-0.2844</v>
       </c>
       <c r="U25" t="n">
-        <v>0.0355</v>
+        <v>0.2321</v>
       </c>
       <c r="V25" t="n">
         <v>-0.8701</v>
@@ -2437,13 +2437,13 @@
         <v>1</v>
       </c>
       <c r="D26" t="n">
-        <v>-4.4728</v>
+        <v>-4.9051</v>
       </c>
       <c r="E26" t="n">
-        <v>-1.0376</v>
+        <v>-1.7507</v>
       </c>
       <c r="F26" t="n">
-        <v>-3.4352</v>
+        <v>-3.1544</v>
       </c>
       <c r="G26" t="n">
         <v>-1.9273</v>
@@ -2482,13 +2482,13 @@
         <v>1.784</v>
       </c>
       <c r="S26" t="n">
-        <v>0.1176</v>
+        <v>-0.3147</v>
       </c>
       <c r="T26" t="n">
-        <v>-0.1172</v>
+        <v>-0.8303</v>
       </c>
       <c r="U26" t="n">
-        <v>0.2348</v>
+        <v>0.5155999999999999</v>
       </c>
       <c r="V26" t="n">
         <v>-1.4737</v>
@@ -2515,13 +2515,13 @@
         <v>1</v>
       </c>
       <c r="D27" t="n">
-        <v>-5.0078</v>
+        <v>-5.4499</v>
       </c>
       <c r="E27" t="n">
-        <v>-4.4175</v>
+        <v>-4.2138</v>
       </c>
       <c r="F27" t="n">
-        <v>-0.5903</v>
+        <v>-1.2361</v>
       </c>
       <c r="G27" t="n">
         <v>-6.2241</v>
@@ -2560,13 +2560,13 @@
         <v>1.9822</v>
       </c>
       <c r="S27" t="n">
-        <v>-0.2068</v>
+        <v>-0.6489</v>
       </c>
       <c r="T27" t="n">
-        <v>-1.7361</v>
+        <v>-1.5324</v>
       </c>
       <c r="U27" t="n">
-        <v>1.5293</v>
+        <v>0.8835</v>
       </c>
       <c r="V27" t="n">
         <v>2.4142</v>
@@ -2593,13 +2593,13 @@
         <v>1</v>
       </c>
       <c r="D28" t="n">
-        <v>-13.3677</v>
+        <v>-12.6886</v>
       </c>
       <c r="E28" t="n">
-        <v>-0.1619000000000002</v>
+        <v>-0.1619999999999999</v>
       </c>
       <c r="F28" t="n">
-        <v>-13.2058</v>
+        <v>-12.5267</v>
       </c>
       <c r="G28" t="n">
         <v>-9.3368</v>
@@ -2638,13 +2638,13 @@
         <v>11.8933</v>
       </c>
       <c r="S28" t="n">
-        <v>-4.698600000000001</v>
+        <v>-4.019500000000001</v>
       </c>
       <c r="T28" t="n">
-        <v>-7.835800000000001</v>
+        <v>-7.835900000000001</v>
       </c>
       <c r="U28" t="n">
-        <v>3.1371</v>
+        <v>3.8164</v>
       </c>
       <c r="V28" t="n">
         <v>4.6323</v>
